--- a/docs/review/packs/chapter-3.3.xlsx
+++ b/docs/review/packs/chapter-3.3.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -2284,7 +2284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Treat a non weight bearing measurement as describing a different task from the weight bearing one, not a more convenient version of it.</t>
+          <t>State the method and the loading condition with any kinematic figure, because the same knee gives different numbers under different methods.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Use the activity pages in this chapter as the normal comparator rather than a single quoted range of motion.</t>
+          <t>Treat a non weight bearing measurement as describing a different task from the weight bearing one, not a more convenient version of it.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Treat kinematics as the language in which a reconstruction's aim is stated.</t>
+          <t>Read a small rotational difference with the measurement error in mind before calling it a finding.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Expect restored laxity without restored motion, and ask about function rather than inferring it from an instrument.</t>
+          <t>Use the activity pages in this chapter as the normal comparator rather than a single quoted range of motion.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -2473,22 +2473,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P1</t>
+          <t>3.3.1-P5</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Expect a cruciate deficient knee to sit and to travel differently rather than only to translate further on testing.</t>
+          <t>Treat kinematics as the language in which a reconstruction's aim is stated.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -2498,22 +2498,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P2</t>
+          <t>3.3.1-P6</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Preserve the posterior horns where possible, on the mechanical ground that they guide the contact path.</t>
+          <t>Expect restored laxity without restored motion, and ask about function rather than inferring it from an instrument.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P3</t>
+          <t>3.3.2-P1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Treat rollback as a design requirement rather than a description.</t>
+          <t>Expect a cruciate deficient knee to sit and to travel differently rather than only to translate further on testing.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P4</t>
+          <t>3.3.2-P2</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Consider paradoxical motion when a well aligned replacement gives poor deep flexion without pain.</t>
+          <t>Preserve the posterior horns where possible, on the mechanical ground that they guide the contact path.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P5</t>
+          <t>3.3.2-P3</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Address slope where it is shifting the contact path rather than treating it as an incidental measurement.</t>
+          <t>Read a rollback figure with its loading condition attached, since unloaded and loaded measurements differ.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2598,22 +2598,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P1</t>
+          <t>3.3.2-P4</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>3.3.3</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Expect a patient to compensate at the hip or the ankle when the knee cannot do its share.</t>
+          <t>Treat rollback as a design requirement rather than a description.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2623,22 +2623,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P2</t>
+          <t>3.3.2-P5</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.3.3</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Treat the limb as a linked chain rather than as a joint.</t>
+          <t>Consider paradoxical motion when a well aligned replacement gives poor deep flexion without pain.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2648,22 +2648,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P3</t>
+          <t>3.3.2-P6</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.3.3</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Non weight bearing laboratory data describes open chain and should not be read across, which is a frequent error in applying kinematic figures.</t>
+          <t>Address slope where it is shifting the contact path rather than treating it as an incidental measurement.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2673,22 +2673,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P4</t>
+          <t>3.3.2-P7</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.3.3</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Assess the hip and the ankle when a closed chain knee task is abnormal, because the chain distributes the problem.</t>
+          <t>Read a design comparison by the task its kinematics were measured in.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P5</t>
+          <t>3.3.3-P1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Expect ground derived rotation to reach the knee in a planted foot, which is the mechanical setting for pivoting injury.</t>
+          <t>Expect a patient to compensate at the hip or the ankle when the knee cannot do its share.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P6</t>
+          <t>3.3.3-P2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Use a closed chain measurement when the question is about function and an open chain one when the question is about the knee alone.</t>
+          <t>Treat the limb as a linked chain rather than as a joint.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2748,7 +2748,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P7</t>
+          <t>3.3.3-P3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>- Non weight bearing data describes open chain and should not be read across.</t>
+          <t>Non weight bearing laboratory data describes open chain and should not be read across, which is a frequent error in applying kinematic figures.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P8</t>
+          <t>3.3.3-P4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Treat closed chain kinematics as the condition most surgical decisions are really about, since patients present with symptoms in standing tasks rather than in seated ones.</t>
+          <t>Assess the hip and the ankle when a closed chain knee task is abnormal, because the chain distributes the problem.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P9</t>
+          <t>3.3.3-P5</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment in a standing long leg film before attributing a closed chain symptom to the soft tissues alone.</t>
+          <t>Expect ground derived rotation to reach the knee in a planted foot, which is the mechanical setting for pivoting injury.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P10</t>
+          <t>3.3.3-P6</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Expect compensation to mask a deficit in a kinematic record, and read the record alongside the examination.</t>
+          <t>Use a closed chain measurement when the question is about function and an open chain one when the question is about the knee alone.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P11</t>
+          <t>3.3.3-P7</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Consider adjacent joint pathology as a cause of knee overload rather than only as a comorbidity.</t>
+          <t>State the chain whenever a range or a translation is recorded.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P1</t>
+          <t>3.3.3-P8</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Expect guarding to reduce the measured laxity, and plan around the larger figure from examination under anaesthetic.</t>
+          <t>- Non weight bearing data describes open chain and should not be read across.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2898,22 +2898,22 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P2</t>
+          <t>3.3.3-P9</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Treat an effusion as a cause of an altered range before attributing the range to a structure.</t>
+          <t>Treat closed chain kinematics as the condition most surgical decisions are really about, since patients present with symptoms in standing tasks rather than in seated ones.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2923,22 +2923,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P3</t>
+          <t>3.3.3-P10</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Keep open chain and closed chain figures in separate columns rather than combining them into one range.</t>
+          <t>Measure alignment in a standing long leg film before attributing a closed chain symptom to the soft tissues alone.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2948,12 +2948,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P4</t>
+          <t>3.3.3-P11</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Treat the open chain measurement as a structural question and the closed chain one as a functional question, then expect them to disagree in the patients who are difficult.</t>
+          <t>Expect compensation to mask a deficit in a kinematic record, and read the record alongside the examination.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2973,12 +2973,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P5</t>
+          <t>3.3.3-P12</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Measure under anaesthetic when the structural question decides the operation.</t>
+          <t>Consider adjacent joint pathology as a cause of knee overload rather than only as a comorbidity.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2998,12 +2998,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P6</t>
+          <t>3.3.3-P13</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Expect a tight open chain measurement to coexist with closed chain symptoms, and counsel accordingly.</t>
+          <t>Set rehabilitation goals in the chain the patient's symptoms occur in.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -3023,7 +3023,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P7</t>
+          <t>3.3.4-P1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Avoid treating a small arthrometer difference as a finding without the instrument's limit of agreement in mind.</t>
+          <t>Expect guarding to reduce the measured laxity, and plan around the larger figure from examination under anaesthetic.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -3048,12 +3048,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P1</t>
+          <t>3.3.4-P2</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Protect and restore full extension after any knee injury or operation, because the locking position depends on the last few degrees.</t>
+          <t>Treat an effusion as a cause of an altered range before attributing the range to a structure.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -3073,12 +3073,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P2</t>
+          <t>3.3.4-P3</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Expect a knee that cannot fully extend to fatigue the quadriceps in standing, and treat the extension rather than the muscle.</t>
+          <t>Keep open chain and closed chain figures in separate columns rather than combining them into one range.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3098,22 +3098,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P3</t>
+          <t>3.3.4-P4</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Avoid quoting terminal rotation as a precise figure, since the published range is wide relative to the quantity.</t>
+          <t>Treat the open chain measurement as a structural question and the closed chain one as a functional question, then expect them to disagree in the patients who are difficult.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -3123,12 +3123,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P4</t>
+          <t>3.3.4-P5</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Treat terminal extension as a design and a technical target.</t>
+          <t>Measure under anaesthetic when the structural question decides the operation.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3148,12 +3148,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P5</t>
+          <t>3.3.4-P6</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Place the femoral tunnel to allow terminal extension, and check it on the table.</t>
+          <t>Expect a tight open chain measurement to coexist with closed chain symptoms, and counsel accordingly.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -3173,12 +3173,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P6</t>
+          <t>3.3.4-P7</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Consider component rotation when a replaced knee loses terminal extension without mechanical obstruction.</t>
+          <t>Stage rehabilitation by the range at which each chain loads the graft rather than by time alone.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -3198,22 +3198,22 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P1</t>
+          <t>3.3.4-P8</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Treat the popliteus as a rotator with a flexion component rather than as a flexor, and its clinical significance follows from the first description.</t>
+          <t>Avoid treating a small arthrometer difference as a finding without the instrument's limit of agreement in mind.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -3223,12 +3223,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P2</t>
+          <t>3.3.5-P1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation at 30 degrees when a posterolateral injury is suspected, since that is where the complex is the restraint.</t>
+          <t>Protect and restore full extension after any knee injury or operation, because the locking position depends on the last few degrees.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -3248,12 +3248,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P3</t>
+          <t>3.3.5-P2</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Expect a corner injury to affect the initiation of flexion as well as rotational stability.</t>
+          <t>Expect a knee that cannot fully extend to fatigue the quadriceps in standing, and treat the extension rather than the muscle.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -3273,12 +3273,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P4</t>
+          <t>3.3.5-P3</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Consider the popliteomeniscal fascicles when a lateral meniscus is hypermobile without a tear.</t>
+          <t>Avoid quoting terminal rotation as a precise figure, since the published range is wide relative to the quantity.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -3298,22 +3298,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P5</t>
+          <t>3.3.5-P4</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Avoid attributing a rotational finding to the popliteus alone, since no clinical test isolates it.</t>
+          <t>Treat terminal extension as a design and a technical target.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -3323,12 +3323,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P6</t>
+          <t>3.3.5-P5</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Treat the popliteus complex as a reconstruction target rather than as a muscle to be noted.</t>
+          <t>Place the femoral tunnel to allow terminal extension, and check it on the table.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -3348,12 +3348,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P7</t>
+          <t>3.3.5-P6</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching holds that anatomic posterolateral reconstruction should address the popliteus tendon, the popliteofibular ligament and the lateral collateral ligament rather than a subset.</t>
+          <t>Consider component rotation when a replaced knee loses terminal extension without mechanical obstruction.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P8</t>
+          <t>3.3.6-P1</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Examine the posterolateral corner in every cruciate injury, since missing it fails the graft.</t>
+          <t>Treat the popliteus as a rotator with a flexion component rather than as a flexor, and its clinical significance follows from the first description.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P9</t>
+          <t>3.3.6-P2</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Address varus alignment before or with a corner reconstruction in a varus limb.</t>
+          <t>Assess rotation at 30 degrees when a posterolateral injury is suspected, since that is where the complex is the restraint.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -3423,12 +3423,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P1</t>
+          <t>3.3.6-P3</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Use the epicondylar axis as the working approximation in surgery and keep its approximate status in mind.</t>
+          <t>Expect a corner injury to affect the initiation of flexion as well as rotational stability.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3448,12 +3448,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P2</t>
+          <t>3.3.6-P4</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Expect a single axis brace or external fixator spanning the knee to fit the limb imperfectly through range.</t>
+          <t>Consider the popliteomeniscal fascicles when a lateral meniscus is hypermobile without a tear.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3473,22 +3473,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P3</t>
+          <t>3.3.6-P5</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Treat the centrode as the design variable that single radius and multi radius implants disagree about.</t>
+          <t>Avoid attributing a rotational finding to the popliteus alone, since no clinical test isolates it.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3498,12 +3498,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P4</t>
+          <t>3.3.6-P6</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Expect deep flexion behaviour to differ between single and multi radius designs on kinematic grounds.</t>
+          <t>Treat the popliteus complex as a reconstruction target rather than as a muscle to be noted.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3523,12 +3523,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P5</t>
+          <t>3.3.6-P7</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Consider component position before design when a replaced knee's motion is wrong.</t>
+          <t>Conventional teaching holds that anatomic posterolateral reconstruction should address the popliteus tendon, the popliteofibular ligament and the lateral collateral ligament rather than a subset.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3548,12 +3548,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P6</t>
+          <t>3.3.6-P8</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Keep intraoperative axis measurement distinct from the functioning knee's behaviour.</t>
+          <t>Examine the posterolateral corner in every cruciate injury, since missing it fails the graft.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P1</t>
+          <t>3.3.6-P9</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Expect symptoms to be angle specific.</t>
+          <t>Address varus alignment before or with a corner reconstruction in a varus limb.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3598,12 +3598,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P2</t>
+          <t>3.3.7-P1</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Examine at 0, 30 and 90 degrees deliberately, because each samples a different restraint set.</t>
+          <t>Use the epicondylar axis as the working approximation in surgery and keep its approximate status in mind.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3623,12 +3623,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P3</t>
+          <t>3.3.7-P2</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Expect a finding to be present at one angle and absent at another, and record the angle rather than the finding alone.</t>
+          <t>Expect a single axis brace or external fixator spanning the knee to fit the limb imperfectly through range.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3648,12 +3648,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P4</t>
+          <t>3.3.7-P3</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Consider deep flexion loading in a patient whose symptoms appear only at the end of range.</t>
+          <t>Read a published centrode with its angular increment and its method attached.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3673,12 +3673,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P5</t>
+          <t>3.3.7-P4</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Treat mid flexion as the zone where reconstructions and replacements fail quietly.</t>
+          <t>Treat the centrode as the design variable that single radius and multi radius implants disagree about.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3698,12 +3698,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P6</t>
+          <t>3.3.7-P5</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Check gaps through mid flexion rather than at extension and 90 degrees alone.</t>
+          <t>Set a hinged external fixator's axis to the epicondylar line, since an off axis hinge translates the joint through range.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3723,12 +3723,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P7</t>
+          <t>3.3.7-P6</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Restore the joint line, since shifting it changes ligament tension through the whole arc.</t>
+          <t>Expect deep flexion behaviour to differ between single and multi radius designs on kinematic grounds.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3748,22 +3748,22 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P1</t>
+          <t>3.3.7-P7</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Expect normal walking in a knee with significant pathology, because the task is undemanding.</t>
+          <t>Consider component position before design when a replaced knee's motion is wrong.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3773,12 +3773,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P2</t>
+          <t>3.3.7-P8</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Treat gait kinematics as the task most patients judge an operation by, and as a weak discriminator between constructs, since walking demands little of the knee.</t>
+          <t>Keep intraoperative axis measurement distinct from the functioning knee's behaviour.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3798,22 +3798,22 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P3</t>
+          <t>3.3.8-P1</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Use gait as the patient's benchmark and not as the test that separates two constructs.</t>
+          <t>Expect symptoms to be angle specific.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3823,22 +3823,22 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P4</t>
+          <t>3.3.8-P2</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Measure or estimate the adduction moment when alignment is the question rather than relying on sagittal kinematics.</t>
+          <t>Examine at 0, 30 and 90 degrees deliberately, because each samples a different restraint set.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3848,22 +3848,22 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P5</t>
+          <t>3.3.8-P3</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Expect habit to outlast the mechanical cause, and rehabilitate accordingly.</t>
+          <t>Expect a finding to be present at one angle and absent at another, and record the angle rather than the finding alone.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3873,12 +3873,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P1</t>
+          <t>3.3.8-P4</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Treat running as a repeated absorb and return cycle.</t>
+          <t>Read a graft's behaviour as angle dependent, since the bundles tighten at different angles.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3898,12 +3898,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P2</t>
+          <t>3.3.8-P5</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Assess running separately from walking when a patient's symptoms are activity specific.</t>
+          <t>Consider deep flexion loading in a patient whose symptoms appear only at the end of range.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3923,22 +3923,22 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P3</t>
+          <t>3.3.8-P6</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Expect patellofemoral symptoms to appear in running before walking, on the loading argument rather than on a structural one.</t>
+          <t>Treat mid flexion as the zone where reconstructions and replacements fail quietly.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3948,22 +3948,22 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P4</t>
+          <t>3.3.8-P7</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Consider fatigue when symptoms appear late in an activity rather than at the start.</t>
+          <t>Check gaps through mid flexion rather than at extension and 90 degrees alone.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3973,12 +3973,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P5</t>
+          <t>3.3.8-P8</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Treat return to running as a mechanical decision rather than a time based one.</t>
+          <t>Restore the joint line, since shifting it changes ligament tension through the whole arc.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3998,12 +3998,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P1</t>
+          <t>3.3.9-P1</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Treat the squat as the clinical test of deep flexion mechanics, and treat its shape as information.</t>
+          <t>Expect normal walking in a knee with significant pathology, because the task is undemanding.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -4023,12 +4023,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P2</t>
+          <t>3.3.9-P2</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Measure ankle dorsiflexion when a squat is limited, before attributing it to the knee.</t>
+          <t>Read coronal and transverse gait quantities with the measurement error in mind.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -4048,22 +4048,22 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P3</t>
+          <t>3.3.9-P3</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Expect posterior horn symptoms to appear in deep flexion and to be absent in mid flexion testing.</t>
+          <t>Treat gait kinematics as the task most patients judge an operation by, and as a weak discriminator between constructs, since walking demands little of the knee.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -4073,22 +4073,22 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P4</t>
+          <t>3.3.9-P4</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as absence of a problem.</t>
+          <t>Use gait as the patient's benchmark and not as the test that separates two constructs.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -4098,12 +4098,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P5</t>
+          <t>3.3.9-P5</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Treat deep flexion as a stated goal with a stated cost.</t>
+          <t>Measure or estimate the adduction moment when alignment is the question rather than relying on sagittal kinematics.</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -4123,12 +4123,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P6</t>
+          <t>3.3.9-P6</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Restore posterior condylar offset, since it limits achievable flexion.</t>
+          <t>Expect habit to outlast the mechanical cause, and rehabilitate accordingly.</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
@@ -4148,12 +4148,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P1</t>
+          <t>3.3.10-P1</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Expect patellofemoral pathology to present on stairs, given the simultaneous rise in angle and quadriceps force.</t>
+          <t>Treat running as a repeated absorb and return cycle.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -4173,12 +4173,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P2</t>
+          <t>3.3.10-P2</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Treat a timed stair test as a performance measure rather than a kinematic one.</t>
+          <t>Assess running separately from walking when a patient's symptoms are activity specific.</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
@@ -4198,22 +4198,22 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P3</t>
+          <t>3.3.10-P3</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Treat stair function as a discriminating outcome measure, since it needs more range and more eccentric control than the tasks most patients recover first.</t>
+          <t>Expect patellofemoral symptoms to appear in running before walking, on the loading argument rather than on a structural one.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -4223,22 +4223,22 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P4</t>
+          <t>3.3.10-P4</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Use stair function rather than level walking when judging whether a knee has recovered.</t>
+          <t>Read two dimensional video coronal measurements cautiously, since rotation confounds them.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
@@ -4248,22 +4248,22 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P5</t>
+          <t>3.3.10-P5</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Consider mid flexion instability in a replaced knee whose only complaint is stairs.</t>
+          <t>Consider fatigue when symptoms appear late in an activity rather than at the start.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -4273,12 +4273,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P6</t>
+          <t>3.3.10-P6</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Exclude quadriceps weakness before attributing stair difficulty to the mechanics.</t>
+          <t>Treat return to running as a mechanical decision rather than a time based one.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
@@ -4298,22 +4298,22 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P1</t>
+          <t>3.3.10-P7</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Assess the hip and trunk when a knee lands in valgus, since the knee position is largely set proximally.</t>
+          <t>Stage return to running by criteria rather than by time after surgery.</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -4323,22 +4323,22 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P2</t>
+          <t>3.3.10-P8</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Use landing tasks in return to sport assessment because they reproduce the injury loading.</t>
+          <t>Correct alignment where repeated single compartment loading is the problem.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
@@ -4348,12 +4348,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P3</t>
+          <t>3.3.10-P9</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Treat landing kinematics as a modifiable risk factor and as an imperfect predictor.</t>
+          <t>State the uncertainty about individual tolerance rather than offering a figure.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -4373,22 +4373,22 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P4</t>
+          <t>3.3.11-P1</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Expect asymmetrical landing kinematics to persist after reconstruction with normal laxity.</t>
+          <t>Treat the squat as the clinical test of deep flexion mechanics, and treat its shape as information.</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
@@ -4398,22 +4398,22 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P1</t>
+          <t>3.3.11-P2</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Treat cutting as the task a rotationally deficient knee fails, which is why rotatory laxity and not translation decides the functional result in a pivoting athlete.</t>
+          <t>Measure ankle dorsiflexion when a squat is limited, before attributing it to the knee.</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -4423,22 +4423,22 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P2</t>
+          <t>3.3.11-P3</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Assess rotatory laxity rather than translation alone when counselling a pivoting athlete.</t>
+          <t>Expect posterior horn symptoms to appear in deep flexion and to be absent in mid flexion testing.</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr"/>
@@ -4448,22 +4448,22 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P3</t>
+          <t>3.3.11-P4</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation in high grade rotatory laxity and in revision, on the mechanics of this task.</t>
+          <t>Read patellofemoral symptoms in squatting as a loading consequence of flexion angle.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -4473,31 +4473,556 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P4</t>
+          <t>3.3.11-P5</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before revising a graft that failed without a new injury.</t>
+          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as absence of a problem.</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
       <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>3.3.11-P6</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>3.3.11</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Treat deep flexion as a stated goal with a stated cost.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>3.3.11-P7</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>3.3.11</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Set the deep flexion goal from the patient's needs rather than from the implant's claim.</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>3.3.11-P8</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>3.3.11</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Restore posterior condylar offset, since it limits achievable flexion.</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12-P1</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Expect patellofemoral pathology to present on stairs, given the simultaneous rise in angle and quadriceps force.</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12-P2</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Treat a timed stair test as a performance measure rather than a kinematic one.</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12-P3</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Treat stair function as a discriminating outcome measure, since it needs more range and more eccentric control than the tasks most patients recover first.</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12-P4</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Use stair function rather than level walking when judging whether a knee has recovered.</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12-P5</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Consider mid flexion instability in a replaced knee whose only complaint is stairs.</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12-P6</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Exclude quadriceps weakness before attributing stair difficulty to the mechanics.</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13-P1</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Assess the hip and trunk when a knee lands in valgus, since the knee position is largely set proximally.</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13-P2</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Read a video frontal plane angle as a screening measure rather than a measurement of valgus.</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13-P3</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Use landing tasks in return to sport assessment because they reproduce the injury loading.</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13-P4</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Treat landing kinematics as a modifiable risk factor and as an imperfect predictor.</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13-P5</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Expect asymmetrical landing kinematics to persist after reconstruction with normal laxity.</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13-P6</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>3.3.13</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>State that screening does not identify the individual at risk, while the population association stands.</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P1</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Read transverse plane cutting data with the measurement error in mind.</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P2</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Treat cutting as the task a rotationally deficient knee fails, which is why rotatory laxity and not translation decides the functional result in a pivoting athlete.</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P3</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Assess rotatory laxity rather than translation alone when counselling a pivoting athlete.</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P4</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Consider lateral augmentation in high grade rotatory laxity and in revision, on the mechanics of this task.</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P5</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Measure slope before revising a graft that failed without a new injury.</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P6</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>State that no assessment reproduces an unanticipated cut when discussing return to sport.</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5568,7 +6093,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>85</f>
+        <f>106</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -5583,7 +6108,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E87,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E108,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -5613,7 +6138,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E87,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E108,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -5625,7 +6150,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E87,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E108,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -5637,7 +6162,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E87,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E108,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -5649,7 +6174,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E87,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E108,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.3.xlsx
+++ b/docs/review/packs/chapter-3.3.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -2284,7 +2284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2523,22 +2523,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P1</t>
+          <t>3.3.1-P7</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Expect a cruciate deficient knee to sit and to travel differently rather than only to translate further on testing.</t>
+          <t>Record the loading condition in any comparison between operated and unoperated sides.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P2</t>
+          <t>3.3.2-P1</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Preserve the posterior horns where possible, on the mechanical ground that they guide the contact path.</t>
+          <t>Expect a cruciate deficient knee to sit and to travel differently rather than only to translate further on testing.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P3</t>
+          <t>3.3.2-P2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Read a rollback figure with its loading condition attached, since unloaded and loaded measurements differ.</t>
+          <t>Preserve the posterior horns where possible, on the mechanical ground that they guide the contact path.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2598,7 +2598,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P4</t>
+          <t>3.3.2-P3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Treat rollback as a design requirement rather than a description.</t>
+          <t>Read a rollback figure with its loading condition attached, since unloaded and loaded measurements differ.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2623,7 +2623,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P5</t>
+          <t>3.3.2-P4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Consider paradoxical motion when a well aligned replacement gives poor deep flexion without pain.</t>
+          <t>Treat rollback as a design requirement rather than a description.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2648,7 +2648,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P6</t>
+          <t>3.3.2-P5</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Address slope where it is shifting the contact path rather than treating it as an incidental measurement.</t>
+          <t>Consider paradoxical motion when a well aligned replacement gives poor deep flexion without pain.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2673,7 +2673,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-P7</t>
+          <t>3.3.2-P6</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Read a design comparison by the task its kinematics were measured in.</t>
+          <t>Address slope where it is shifting the contact path rather than treating it as an incidental measurement.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2698,22 +2698,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P1</t>
+          <t>3.3.2-P7</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3.3.3</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Expect a patient to compensate at the hip or the ankle when the knee cannot do its share.</t>
+          <t>Read a design comparison by the task its kinematics were measured in.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P2</t>
+          <t>3.3.3-P1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Treat the limb as a linked chain rather than as a joint.</t>
+          <t>Expect a patient to compensate at the hip or the ankle when the knee cannot do its share.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2748,7 +2748,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P3</t>
+          <t>3.3.3-P2</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Non weight bearing laboratory data describes open chain and should not be read across, which is a frequent error in applying kinematic figures.</t>
+          <t>Treat the limb as a linked chain rather than as a joint.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P4</t>
+          <t>3.3.3-P3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Assess the hip and the ankle when a closed chain knee task is abnormal, because the chain distributes the problem.</t>
+          <t>Non weight bearing laboratory data describes open chain and should not be read across, which is a frequent error in applying kinematic figures.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P5</t>
+          <t>3.3.3-P4</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Expect ground derived rotation to reach the knee in a planted foot, which is the mechanical setting for pivoting injury.</t>
+          <t>Assess the hip and the ankle when a closed chain knee task is abnormal, because the chain distributes the problem.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P6</t>
+          <t>3.3.3-P5</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Use a closed chain measurement when the question is about function and an open chain one when the question is about the knee alone.</t>
+          <t>Expect ground derived rotation to reach the knee in a planted foot, which is the mechanical setting for pivoting injury.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P7</t>
+          <t>3.3.3-P6</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>State the chain whenever a range or a translation is recorded.</t>
+          <t>Use a closed chain measurement when the question is about function and an open chain one when the question is about the knee alone.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2873,7 +2873,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P8</t>
+          <t>3.3.3-P7</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>- Non weight bearing data describes open chain and should not be read across.</t>
+          <t>State the chain whenever a range or a translation is recorded.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2898,7 +2898,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P9</t>
+          <t>3.3.3-P8</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Treat closed chain kinematics as the condition most surgical decisions are really about, since patients present with symptoms in standing tasks rather than in seated ones.</t>
+          <t>- Non weight bearing data describes open chain and should not be read across.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P10</t>
+          <t>3.3.3-P9</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment in a standing long leg film before attributing a closed chain symptom to the soft tissues alone.</t>
+          <t>Treat closed chain kinematics as the condition most surgical decisions are really about, since patients present with symptoms in standing tasks rather than in seated ones.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P11</t>
+          <t>3.3.3-P10</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Expect compensation to mask a deficit in a kinematic record, and read the record alongside the examination.</t>
+          <t>Measure alignment in a standing long leg film before attributing a closed chain symptom to the soft tissues alone.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2973,7 +2973,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P12</t>
+          <t>3.3.3-P11</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Consider adjacent joint pathology as a cause of knee overload rather than only as a comorbidity.</t>
+          <t>Expect compensation to mask a deficit in a kinematic record, and read the record alongside the examination.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.3.3-P13</t>
+          <t>3.3.3-P12</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Set rehabilitation goals in the chain the patient's symptoms occur in.</t>
+          <t>Consider adjacent joint pathology as a cause of knee overload rather than only as a comorbidity.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -3023,22 +3023,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P1</t>
+          <t>3.3.3-P13</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Expect guarding to reduce the measured laxity, and plan around the larger figure from examination under anaesthetic.</t>
+          <t>Set rehabilitation goals in the chain the patient's symptoms occur in.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -3048,7 +3048,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P2</t>
+          <t>3.3.4-P1</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Treat an effusion as a cause of an altered range before attributing the range to a structure.</t>
+          <t>Record the hip position when measuring open chain range or strength, since the two joint muscles change the answer.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P3</t>
+          <t>3.3.4-P2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Keep open chain and closed chain figures in separate columns rather than combining them into one range.</t>
+          <t>Expect guarding to reduce the measured laxity, and plan around the larger figure from examination under anaesthetic.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3098,7 +3098,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P4</t>
+          <t>3.3.4-P3</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Treat the open chain measurement as a structural question and the closed chain one as a functional question, then expect them to disagree in the patients who are difficult.</t>
+          <t>Treat an effusion as a cause of an altered range before attributing the range to a structure.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -3123,7 +3123,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P5</t>
+          <t>3.3.4-P4</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Measure under anaesthetic when the structural question decides the operation.</t>
+          <t>Keep open chain and closed chain figures in separate columns rather than combining them into one range.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3148,7 +3148,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P6</t>
+          <t>3.3.4-P5</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Expect a tight open chain measurement to coexist with closed chain symptoms, and counsel accordingly.</t>
+          <t>Treat the open chain measurement as a structural question and the closed chain one as a functional question, then expect them to disagree in the patients who are difficult.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -3173,7 +3173,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P7</t>
+          <t>3.3.4-P6</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Stage rehabilitation by the range at which each chain loads the graft rather than by time alone.</t>
+          <t>Measure under anaesthetic when the structural question decides the operation.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -3198,7 +3198,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-P8</t>
+          <t>3.3.4-P7</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Avoid treating a small arthrometer difference as a finding without the instrument's limit of agreement in mind.</t>
+          <t>Expect a tight open chain measurement to coexist with closed chain symptoms, and counsel accordingly.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -3223,22 +3223,22 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P1</t>
+          <t>3.3.4-P8</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Protect and restore full extension after any knee injury or operation, because the locking position depends on the last few degrees.</t>
+          <t>Stage rehabilitation by the range at which each chain loads the graft rather than by time alone.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -3248,22 +3248,22 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P2</t>
+          <t>3.3.4-P9</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Expect a knee that cannot fully extend to fatigue the quadriceps in standing, and treat the extension rather than the muscle.</t>
+          <t>Avoid treating a small arthrometer difference as a finding without the instrument's limit of agreement in mind.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -3273,7 +3273,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P3</t>
+          <t>3.3.5-P1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Avoid quoting terminal rotation as a precise figure, since the published range is wide relative to the quantity.</t>
+          <t>Protect and restore full extension after any knee injury or operation, because the locking position depends on the last few degrees.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -3298,7 +3298,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P4</t>
+          <t>3.3.5-P2</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Treat terminal extension as a design and a technical target.</t>
+          <t>Expect a knee that cannot fully extend to fatigue the quadriceps in standing, and treat the extension rather than the muscle.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P5</t>
+          <t>3.3.5-P3</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Place the femoral tunnel to allow terminal extension, and check it on the table.</t>
+          <t>Avoid quoting terminal rotation as a precise figure, since the published range is wide relative to the quantity.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-P6</t>
+          <t>3.3.5-P4</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Consider component rotation when a replaced knee loses terminal extension without mechanical obstruction.</t>
+          <t>Treat terminal extension as a design and a technical target.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -3373,22 +3373,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P1</t>
+          <t>3.3.5-P5</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Treat the popliteus as a rotator with a flexion component rather than as a flexor, and its clinical significance follows from the first description.</t>
+          <t>Place the femoral tunnel to allow terminal extension, and check it on the table.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -3398,22 +3398,22 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P2</t>
+          <t>3.3.5-P6</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation at 30 degrees when a posterolateral injury is suspected, since that is where the complex is the restraint.</t>
+          <t>Consider component rotation when a replaced knee loses terminal extension without mechanical obstruction.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P3</t>
+          <t>3.3.6-P1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Expect a corner injury to affect the initiation of flexion as well as rotational stability.</t>
+          <t>Treat the popliteus as a rotator with a flexion component rather than as a flexor, and its clinical significance follows from the first description.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P4</t>
+          <t>3.3.6-P2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Consider the popliteomeniscal fascicles when a lateral meniscus is hypermobile without a tear.</t>
+          <t>Assess rotation at 30 degrees when a posterolateral injury is suspected, since that is where the complex is the restraint.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3473,7 +3473,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P5</t>
+          <t>3.3.6-P3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Avoid attributing a rotational finding to the popliteus alone, since no clinical test isolates it.</t>
+          <t>Expect a corner injury to affect the initiation of flexion as well as rotational stability.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P6</t>
+          <t>3.3.6-P4</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Treat the popliteus complex as a reconstruction target rather than as a muscle to be noted.</t>
+          <t>Consider the popliteomeniscal fascicles when a lateral meniscus is hypermobile without a tear.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P7</t>
+          <t>3.3.6-P5</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching holds that anatomic posterolateral reconstruction should address the popliteus tendon, the popliteofibular ligament and the lateral collateral ligament rather than a subset.</t>
+          <t>Avoid attributing a rotational finding to the popliteus alone, since no clinical test isolates it.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P8</t>
+          <t>3.3.6-P6</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Examine the posterolateral corner in every cruciate injury, since missing it fails the graft.</t>
+          <t>Treat the popliteus complex as a reconstruction target rather than as a muscle to be noted.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-P9</t>
+          <t>3.3.6-P7</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Address varus alignment before or with a corner reconstruction in a varus limb.</t>
+          <t>Conventional teaching holds that anatomic posterolateral reconstruction should address the popliteus tendon, the popliteofibular ligament and the lateral collateral ligament rather than a subset.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3598,22 +3598,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P1</t>
+          <t>3.3.6-P8</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Use the epicondylar axis as the working approximation in surgery and keep its approximate status in mind.</t>
+          <t>Examine the posterolateral corner in every cruciate injury, since missing it fails the graft.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3623,22 +3623,22 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P2</t>
+          <t>3.3.6-P9</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Expect a single axis brace or external fixator spanning the knee to fit the limb imperfectly through range.</t>
+          <t>Address varus alignment before or with a corner reconstruction in a varus limb.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3648,7 +3648,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P3</t>
+          <t>3.3.7-P1</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Read a published centrode with its angular increment and its method attached.</t>
+          <t>Use the epicondylar axis as the working approximation in surgery and keep its approximate status in mind.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P4</t>
+          <t>3.3.7-P2</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Treat the centrode as the design variable that single radius and multi radius implants disagree about.</t>
+          <t>Expect a single axis brace or external fixator spanning the knee to fit the limb imperfectly through range.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P5</t>
+          <t>3.3.7-P3</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Set a hinged external fixator's axis to the epicondylar line, since an off axis hinge translates the joint through range.</t>
+          <t>Read a published centrode with its angular increment and its method attached.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3723,7 +3723,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P6</t>
+          <t>3.3.7-P4</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Expect deep flexion behaviour to differ between single and multi radius designs on kinematic grounds.</t>
+          <t>Treat the centrode as the design variable that single radius and multi radius implants disagree about.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P7</t>
+          <t>3.3.7-P5</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Consider component position before design when a replaced knee's motion is wrong.</t>
+          <t>Set a hinged external fixator's axis to the epicondylar line, since an off axis hinge translates the joint through range.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.3.7-P8</t>
+          <t>3.3.7-P6</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Keep intraoperative axis measurement distinct from the functioning knee's behaviour.</t>
+          <t>Expect deep flexion behaviour to differ between single and multi radius designs on kinematic grounds.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3798,22 +3798,22 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P1</t>
+          <t>3.3.7-P7</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Expect symptoms to be angle specific.</t>
+          <t>Consider component position before design when a replaced knee's motion is wrong.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3823,22 +3823,22 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P2</t>
+          <t>3.3.7-P8</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Examine at 0, 30 and 90 degrees deliberately, because each samples a different restraint set.</t>
+          <t>Keep intraoperative axis measurement distinct from the functioning knee's behaviour.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P3</t>
+          <t>3.3.8-P1</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Expect a finding to be present at one angle and absent at another, and record the angle rather than the finding alone.</t>
+          <t>Expect symptoms to be angle specific.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3873,7 +3873,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P4</t>
+          <t>3.3.8-P2</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Read a graft's behaviour as angle dependent, since the bundles tighten at different angles.</t>
+          <t>Examine at 0, 30 and 90 degrees deliberately, because each samples a different restraint set.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P5</t>
+          <t>3.3.8-P3</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Consider deep flexion loading in a patient whose symptoms appear only at the end of range.</t>
+          <t>Expect a finding to be present at one angle and absent at another, and record the angle rather than the finding alone.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P6</t>
+          <t>3.3.8-P4</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Treat mid flexion as the zone where reconstructions and replacements fail quietly.</t>
+          <t>Read a graft's behaviour as angle dependent, since the bundles tighten at different angles.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3948,7 +3948,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P7</t>
+          <t>3.3.8-P5</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Check gaps through mid flexion rather than at extension and 90 degrees alone.</t>
+          <t>Consider deep flexion loading in a patient whose symptoms appear only at the end of range.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3973,7 +3973,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-P8</t>
+          <t>3.3.8-P6</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Restore the joint line, since shifting it changes ligament tension through the whole arc.</t>
+          <t>Treat mid flexion as the zone where reconstructions and replacements fail quietly.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3998,22 +3998,22 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P1</t>
+          <t>3.3.8-P7</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Expect normal walking in a knee with significant pathology, because the task is undemanding.</t>
+          <t>Check gaps through mid flexion rather than at extension and 90 degrees alone.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -4023,22 +4023,22 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P2</t>
+          <t>3.3.8-P8</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Read coronal and transverse gait quantities with the measurement error in mind.</t>
+          <t>Restore the joint line, since shifting it changes ligament tension through the whole arc.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P3</t>
+          <t>3.3.9-P1</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Treat gait kinematics as the task most patients judge an operation by, and as a weak discriminator between constructs, since walking demands little of the knee.</t>
+          <t>Expect normal walking in a knee with significant pathology, because the task is undemanding.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -4073,7 +4073,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P4</t>
+          <t>3.3.9-P2</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Use gait as the patient's benchmark and not as the test that separates two constructs.</t>
+          <t>Read coronal and transverse gait quantities with the measurement error in mind.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P5</t>
+          <t>3.3.9-P3</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Measure or estimate the adduction moment when alignment is the question rather than relying on sagittal kinematics.</t>
+          <t>Treat gait kinematics as the task most patients judge an operation by, and as a weak discriminator between constructs, since walking demands little of the knee.</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -4123,7 +4123,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-P6</t>
+          <t>3.3.9-P4</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Expect habit to outlast the mechanical cause, and rehabilitate accordingly.</t>
+          <t>Use gait as the patient's benchmark and not as the test that separates two constructs.</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
@@ -4148,22 +4148,22 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P1</t>
+          <t>3.3.9-P5</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Treat running as a repeated absorb and return cycle.</t>
+          <t>Measure or estimate the adduction moment when alignment is the question rather than relying on sagittal kinematics.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -4173,22 +4173,22 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P2</t>
+          <t>3.3.9-P6</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Assess running separately from walking when a patient's symptoms are activity specific.</t>
+          <t>Expect habit to outlast the mechanical cause, and rehabilitate accordingly.</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
@@ -4198,7 +4198,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P3</t>
+          <t>3.3.10-P1</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Expect patellofemoral symptoms to appear in running before walking, on the loading argument rather than on a structural one.</t>
+          <t>Treat running as a repeated absorb and return cycle.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -4223,7 +4223,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P4</t>
+          <t>3.3.10-P2</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Read two dimensional video coronal measurements cautiously, since rotation confounds them.</t>
+          <t>Assess running separately from walking when a patient's symptoms are activity specific.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P5</t>
+          <t>3.3.10-P3</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Consider fatigue when symptoms appear late in an activity rather than at the start.</t>
+          <t>Expect patellofemoral symptoms to appear in running before walking, on the loading argument rather than on a structural one.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P6</t>
+          <t>3.3.10-P4</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Treat return to running as a mechanical decision rather than a time based one.</t>
+          <t>Read two dimensional video coronal measurements cautiously, since rotation confounds them.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P7</t>
+          <t>3.3.10-P5</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Stage return to running by criteria rather than by time after surgery.</t>
+          <t>Consider fatigue when symptoms appear late in an activity rather than at the start.</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P8</t>
+          <t>3.3.10-P6</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment where repeated single compartment loading is the problem.</t>
+          <t>Treat return to running as a mechanical decision rather than a time based one.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-P9</t>
+          <t>3.3.10-P7</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>State the uncertainty about individual tolerance rather than offering a figure.</t>
+          <t>Stage return to running by criteria rather than by time after surgery.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -4373,22 +4373,22 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P1</t>
+          <t>3.3.10-P8</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Treat the squat as the clinical test of deep flexion mechanics, and treat its shape as information.</t>
+          <t>Correct alignment where repeated single compartment loading is the problem.</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
@@ -4398,22 +4398,22 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P2</t>
+          <t>3.3.10-P9</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Measure ankle dorsiflexion when a squat is limited, before attributing it to the knee.</t>
+          <t>State the uncertainty about individual tolerance rather than offering a figure.</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -4423,7 +4423,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P3</t>
+          <t>3.3.11-P1</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Expect posterior horn symptoms to appear in deep flexion and to be absent in mid flexion testing.</t>
+          <t>Treat the squat as the clinical test of deep flexion mechanics, and treat its shape as information.</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P4</t>
+          <t>3.3.11-P2</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Read patellofemoral symptoms in squatting as a loading consequence of flexion angle.</t>
+          <t>Measure ankle dorsiflexion when a squat is limited, before attributing it to the knee.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P5</t>
+          <t>3.3.11-P3</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as absence of a problem.</t>
+          <t>Expect posterior horn symptoms to appear in deep flexion and to be absent in mid flexion testing.</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P6</t>
+          <t>3.3.11-P4</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Treat deep flexion as a stated goal with a stated cost.</t>
+          <t>Read patellofemoral symptoms in squatting as a loading consequence of flexion angle.</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -4523,7 +4523,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P7</t>
+          <t>3.3.11-P5</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Set the deep flexion goal from the patient's needs rather than from the implant's claim.</t>
+          <t>Treat the thinness of the deep flexion literature as a limit on confidence rather than as absence of a problem.</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-P8</t>
+          <t>3.3.11-P6</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Restore posterior condylar offset, since it limits achievable flexion.</t>
+          <t>Treat deep flexion as a stated goal with a stated cost.</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
@@ -4573,22 +4573,22 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P1</t>
+          <t>3.3.11-P7</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Expect patellofemoral pathology to present on stairs, given the simultaneous rise in angle and quadriceps force.</t>
+          <t>Set the deep flexion goal from the patient's needs rather than from the implant's claim.</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr"/>
@@ -4598,22 +4598,22 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P2</t>
+          <t>3.3.11-P8</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Treat a timed stair test as a performance measure rather than a kinematic one.</t>
+          <t>Restore posterior condylar offset, since it limits achievable flexion.</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
@@ -4623,12 +4623,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P3</t>
+          <t>3.3.11-P9</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Treat stair function as a discriminating outcome measure, since it needs more range and more eccentric control than the tasks most patients recover first.</t>
+          <t>Counsel that measured range and the ability to kneel correlate imperfectly.</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P4</t>
+          <t>3.3.12-P1</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Use stair function rather than level walking when judging whether a knee has recovered.</t>
+          <t>Ask about stairs separately in each direction, because the two directions test different things.</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
@@ -4673,7 +4673,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P5</t>
+          <t>3.3.12-P2</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Consider mid flexion instability in a replaced knee whose only complaint is stairs.</t>
+          <t>Record the direction, the step height and whether a handrail was used when documenting stair ability.</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr"/>
@@ -4698,7 +4698,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-P6</t>
+          <t>3.3.12-P3</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Exclude quadriceps weakness before attributing stair difficulty to the mechanics.</t>
+          <t>Expect patellofemoral pathology to present on stairs, given the simultaneous rise in angle and quadriceps force.</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr"/>
@@ -4723,12 +4723,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P1</t>
+          <t>3.3.12-P4</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.12</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Assess the hip and trunk when a knee lands in valgus, since the knee position is largely set proximally.</t>
+          <t>Treat a timed stair test as a performance measure rather than a kinematic one.</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
@@ -4748,22 +4748,22 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P2</t>
+          <t>3.3.12-P5</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.12</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Read a video frontal plane angle as a screening measure rather than a measurement of valgus.</t>
+          <t>Treat stair function as a discriminating outcome measure, since it needs more range and more eccentric control than the tasks most patients recover first.</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
@@ -4773,22 +4773,22 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P3</t>
+          <t>3.3.12-P6</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.12</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Use landing tasks in return to sport assessment because they reproduce the injury loading.</t>
+          <t>Use stair function rather than level walking when judging whether a knee has recovered.</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr"/>
@@ -4798,12 +4798,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P4</t>
+          <t>3.3.12-P7</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.12</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Treat landing kinematics as a modifiable risk factor and as an imperfect predictor.</t>
+          <t>Consider mid flexion instability in a replaced knee whose only complaint is stairs.</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -4823,12 +4823,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P5</t>
+          <t>3.3.12-P8</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>3.3.13</t>
+          <t>3.3.12</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Expect asymmetrical landing kinematics to persist after reconstruction with normal laxity.</t>
+          <t>Exclude quadriceps weakness before attributing stair difficulty to the mechanics.</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
@@ -4848,7 +4848,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>3.3.13-P6</t>
+          <t>3.3.13-P1</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>State that screening does not identify the individual at risk, while the population association stands.</t>
+          <t>Assess the hip and trunk when a knee lands in valgus, since the knee position is largely set proximally.</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
@@ -4873,12 +4873,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P1</t>
+          <t>3.3.13-P2</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.13</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Read transverse plane cutting data with the measurement error in mind.</t>
+          <t>Read a video frontal plane angle as a screening measure rather than a measurement of valgus.</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
@@ -4898,22 +4898,22 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P2</t>
+          <t>3.3.13-P3</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.13</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Treat cutting as the task a rotationally deficient knee fails, which is why rotatory laxity and not translation decides the functional result in a pivoting athlete.</t>
+          <t>Use landing tasks in return to sport assessment because they reproduce the injury loading.</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
@@ -4923,12 +4923,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P3</t>
+          <t>3.3.13-P4</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.13</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Assess rotatory laxity rather than translation alone when counselling a pivoting athlete.</t>
+          <t>Treat landing kinematics as a modifiable risk factor and as an imperfect predictor.</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
@@ -4948,12 +4948,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P4</t>
+          <t>3.3.13-P5</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.13</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation in high grade rotatory laxity and in revision, on the mechanics of this task.</t>
+          <t>Expect asymmetrical landing kinematics to persist after reconstruction with normal laxity.</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
@@ -4973,12 +4973,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P5</t>
+          <t>3.3.13-P6</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>3.3.14</t>
+          <t>3.3.13</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before revising a graft that failed without a new injury.</t>
+          <t>State that screening does not identify the individual at risk, while the population association stands.</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
@@ -4998,7 +4998,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>3.3.14-P6</t>
+          <t>3.3.14-P1</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -5008,21 +5008,146 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>State that no assessment reproduces an unanticipated cut when discussing return to sport.</t>
+          <t>Read transverse plane cutting data with the measurement error in mind.</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P2</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Treat cutting as the task a rotationally deficient knee fails, which is why rotatory laxity and not translation decides the functional result in a pivoting athlete.</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P3</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Assess rotatory laxity rather than translation alone when counselling a pivoting athlete.</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P4</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Consider lateral augmentation in high grade rotatory laxity and in revision, on the mechanics of this task.</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P5</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Measure slope before revising a graft that failed without a new injury.</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14-P6</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>3.3.14</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>State that no assessment reproduces an unanticipated cut when discussing return to sport.</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6093,7 +6218,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>106</f>
+        <f>111</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -6108,7 +6233,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E108,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E113,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -6138,7 +6263,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E108,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E113,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -6150,7 +6275,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E108,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E113,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -6162,7 +6287,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E108,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E113,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -6174,7 +6299,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E108,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E113,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.3.xlsx
+++ b/docs/review/packs/chapter-3.3.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -5161,7 +5161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5257,27 +5257,27 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>3.3.2-F1</t>
+          <t>3.3.1-F1</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>20 to 30 degrees</t>
+          <t>six degrees</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching describes rolling as dominant through roughly the first 20 to 30 degrees of flexion, with gliding taking an increasing share beyond that.</t>
+          <t>3.2.1 names the six degrees of freedom this chapter then describes through range.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
@@ -5287,12 +5287,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-F1</t>
+          <t>3.3.2-F1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>25 to 30 degrees</t>
+          <t>20 to 30 degrees</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives roughly 25 to 30 degrees of total axial rotation at 90 degrees of flexion in open chain, falling to near zero in full extension.</t>
+          <t>Conventional teaching describes rolling as dominant through roughly the first 20 to 30 degrees of flexion, with gliding taking an increasing share beyond that.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
@@ -5317,7 +5317,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>3.3.4-F2</t>
+          <t>3.3.4-F1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>90 degrees</t>
+          <t>25 to 30 degrees</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -5347,27 +5347,27 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-F1</t>
+          <t>3.3.4-F2</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>90 degrees</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Through roughly the last 30 degrees of extension the tibia rotates externally relative to the femur.</t>
+          <t>Conventional teaching gives roughly 25 to 30 degrees of total axial rotation at 90 degrees of flexion in open chain, falling to near zero in full extension.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
@@ -5377,7 +5377,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>3.3.5-F2</t>
+          <t>3.3.5-F1</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>5 to 10 degrees</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives about 5 to 10 degrees of rotation.</t>
+          <t>Through roughly the last 30 degrees of extension the tibia rotates externally relative to the femur.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
@@ -5407,27 +5407,27 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3.3.6-F1</t>
+          <t>3.3.5-F2</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>5 to 10 degrees</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Posterolateral corner injury, which usually involves the popliteus complex and alters external rotation at 30 degrees.</t>
+          <t>Conventional teaching gives about 5 to 10 degrees of rotation.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -5437,23 +5437,27 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F1</t>
+          <t>3.3.6-F1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3.3.8</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
+          <t>3.3.6</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>The knee is a different joint at 0, 30, 90 and 130 degrees.</t>
+          <t>Posterolateral corner injury, which usually involves the popliteus complex and alters external rotation at 30 degrees.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
@@ -5463,7 +5467,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F2</t>
+          <t>3.3.8-F1</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -5474,7 +5478,7 @@
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5489,7 +5493,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F3</t>
+          <t>3.3.8-F2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -5500,7 +5504,7 @@
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>90 and 130 degrees</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -5515,7 +5519,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F4</t>
+          <t>3.3.8-F3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -5523,19 +5527,15 @@
           <t>3.3.8</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>medical_student</t>
-        </is>
-      </c>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>20 to 30 degrees</t>
+          <t>90 and 130 degrees</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Through roughly 20 to 30 degrees the knee unlocks and the bony contribution to stability falls away, handing over to the ligaments.</t>
+          <t>The knee is a different joint at 0, 30, 90 and 130 degrees.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
@@ -5545,7 +5545,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F5</t>
+          <t>3.3.8-F4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>30 to 90 degrees</t>
+          <t>20 to 30 degrees</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Through mid flexion, roughly 30 to 90 degrees, rotation and translation are at their greatest and the ligaments are the limit.</t>
+          <t>Through roughly 20 to 30 degrees the knee unlocks and the bony contribution to stability falls away, handing over to the ligaments.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F6</t>
+          <t>3.3.8-F5</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>120 degrees</t>
+          <t>30 to 90 degrees</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Beyond about 120 degrees the contact moves to the posterior condyles, the surfaces are small and highly loaded, and the posterior soft tissues take a share again.</t>
+          <t>Through mid flexion, roughly 30 to 90 degrees, rotation and translation are at their greatest and the ligaments are the limit.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
@@ -5605,7 +5605,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F7</t>
+          <t>3.3.8-F6</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -5620,13 +5620,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>30
-degrees</t>
+          <t>120 degrees</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Test at more than one angle, because a structure that is the limit at 30 degrees may contribute little at 90.</t>
+          <t>Beyond about 120 degrees the contact moves to the posterior condyles, the surfaces are small and highly loaded, and the posterior soft tissues take a share again.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
@@ -5636,7 +5635,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F8</t>
+          <t>3.3.8-F7</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -5651,7 +5650,8 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30
+degrees</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -5666,7 +5666,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F9</t>
+          <t>3.3.8-F8</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -5676,17 +5676,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>20 degrees</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Zero to about 20 degrees: maximal congruence, terminal rotation, bony contribution greatest, posterior capsule and collateral structures taut.</t>
+          <t>Test at more than one angle, because a structure that is the limit at 30 degrees may contribute little at 90.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -5696,7 +5696,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F10</t>
+          <t>3.3.8-F9</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>30 and 90 degrees</t>
+          <t>20 degrees</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Examine at 0, 30 and 90 degrees deliberately, because each samples a different restraint set.</t>
+          <t>Zero to about 20 degrees: maximal congruence, terminal rotation, bony contribution greatest, posterior capsule and collateral structures taut.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -5726,7 +5726,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F11</t>
+          <t>3.3.8-F10</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -5736,17 +5736,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>30 to 60 degrees</t>
+          <t>30 and 90 degrees</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Mid flexion instability after replacement is described as a laxity at 30 to 60 degrees with a stable knee in extension and in flexion, and conventional teaching attributes it to femoral component position and to the radius of curvature.</t>
+          <t>Examine at 0, 30 and 90 degrees deliberately, because each samples a different restraint set.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.3.8-F12</t>
+          <t>3.3.8-F11</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>90 degrees</t>
+          <t>30 to 60 degrees</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Check gaps through mid flexion rather than at extension and 90 degrees alone.</t>
+          <t>Mid flexion instability after replacement is described as a laxity at 30 to 60 degrees with a stable knee in extension and in flexion, and conventional teaching attributes it to femoral component position and to the radius of curvature.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -5786,27 +5786,27 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-F1</t>
+          <t>3.3.8-F12</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.3.9</t>
+          <t>3.3.8</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>60 per cent</t>
+          <t>90 degrees</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives stance about 60 per cent of the cycle and swing about 40.</t>
+          <t>Check gaps through mid flexion rather than at extension and 90 degrees alone.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -5816,7 +5816,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-F2</t>
+          <t>3.3.9-F1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60 per cent</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-F3</t>
+          <t>3.3.9-F2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>15 to 20 degrees</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives the first wave as roughly 15 to 20 degrees of flexion during loading response, returning towards extension by mid stance.</t>
+          <t>Conventional teaching gives stance about 60 per cent of the cycle and swing about 40.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
@@ -5876,7 +5876,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-F4</t>
+          <t>3.3.9-F3</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>60 degrees</t>
+          <t>15 to 20 degrees</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The second wave reaches roughly 60 degrees in swing, which is the peak of the whole cycle and takes almost no muscle work to achieve.</t>
+          <t>Conventional teaching gives the first wave as roughly 15 to 20 degrees of flexion during loading response, returning towards extension by mid stance.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -5906,7 +5906,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-F5</t>
+          <t>3.3.9-F4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60 degrees</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>- Conventional teaching gives 15 to 20 degrees in stance and about 60 in swing.</t>
+          <t>The second wave reaches roughly 60 degrees in swing, which is the peak of the whole cycle and takes almost no muscle work to achieve.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.3.9-F6</t>
+          <t>3.3.9-F5</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5 degrees</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>At initial contact the knee is near full extension, conventionally within about 5 degrees.</t>
+          <t>- Conventional teaching gives 15 to 20 degrees in stance and about 60 in swing.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -5966,27 +5966,27 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-F1</t>
+          <t>3.3.9-F6</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.3.10</t>
+          <t>3.3.9</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>20 degrees</t>
+          <t>5 degrees</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives roughly 20 degrees at initial contact in running, against near extension in walking.</t>
+          <t>At initial contact the knee is near full extension, conventionally within about 5 degrees.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-F2</t>
+          <t>3.3.10-F1</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>40 to 45 degrees</t>
+          <t>20 degrees</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Stance flexion then increases to roughly 40 to 45 degrees, which is more than double the walking wave and under a larger load.</t>
+          <t>Conventional teaching gives roughly 20 degrees at initial contact in running, against near extension in walking.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -6026,7 +6026,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.3.10-F3</t>
+          <t>3.3.10-F2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>90 to 130 degrees</t>
+          <t>40 to 45 degrees</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives roughly 90 to 130 degrees depending on speed, since the heel rises towards the buttock as speed increases.</t>
+          <t>Stance flexion then increases to roughly 40 to 45 degrees, which is more than double the walking wave and under a larger load.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -6056,12 +6056,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-F1</t>
+          <t>3.3.10-F3</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.3.11</t>
+          <t>3.3.10</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -6071,13 +6071,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>100
-degrees</t>
+          <t>90 to 130 degrees</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Flexion proceeds from full extension towards deep flexion, commonly past 100 degrees and in a full squat beyond 130.</t>
+          <t>Conventional teaching gives roughly 90 to 130 degrees depending on speed, since the heel rises towards the buttock as speed increases.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -6087,7 +6086,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-F2</t>
+          <t>3.3.11-F1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -6102,7 +6101,8 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100
+degrees</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -6117,7 +6117,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.3.11-F3</t>
+          <t>3.3.11-F2</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>120 degrees</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Beyond roughly 120 degrees the contact moves onto the posterior condyles, where the surfaces are smaller and the load per unit area is higher.</t>
+          <t>Flexion proceeds from full extension towards deep flexion, commonly past 100 degrees and in a full squat beyond 130.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -6147,12 +6147,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.3.12-F1</t>
+          <t>3.3.11-F3</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.3.12</t>
+          <t>3.3.11</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -6162,21 +6162,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>80 to 90 degrees</t>
+          <t>120 degrees</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives peak knee flexion on stairs as roughly 80 to 90 degrees, considerably more than walking on the level.</t>
+          <t>Beyond roughly 120 degrees the contact moves onto the posterior condyles, where the surfaces are smaller and the load per unit area is higher.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12-F1</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>3.3.12</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>80 to 90 degrees</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Conventional teaching gives peak knee flexion on stairs as roughly 80 to 90 degrees, considerably more than walking on the level.</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F3:F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: VERIFIED, CORRECTED, REMOVED" type="list">
+    <dataValidation sqref="F3:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: VERIFIED, CORRECTED, REMOVED" type="list">
       <formula1>"VERIFIED,CORRECTED,REMOVED"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6222,7 +6252,7 @@
         <v/>
       </c>
       <c r="C2" s="3">
-        <f>31</f>
+        <f>32</f>
         <v/>
       </c>
     </row>
@@ -6237,7 +6267,7 @@
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIF(Measurements!F3:F33,"&lt;&gt;")</f>
+        <f>COUNTIF(Measurements!F3:F34,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -6312,7 +6342,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3">
-        <f>COUNTIF(Measurements!F3:F33,"VERIFIED")</f>
+        <f>COUNTIF(Measurements!F3:F34,"VERIFIED")</f>
         <v/>
       </c>
     </row>
@@ -6324,7 +6354,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr"/>
       <c r="C10" s="3">
-        <f>COUNTIF(Measurements!F3:F33,"CORRECTED")</f>
+        <f>COUNTIF(Measurements!F3:F34,"CORRECTED")</f>
         <v/>
       </c>
     </row>
@@ -6336,7 +6366,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="3">
-        <f>COUNTIF(Measurements!F3:F33,"REMOVED")</f>
+        <f>COUNTIF(Measurements!F3:F34,"REMOVED")</f>
         <v/>
       </c>
     </row>
